--- a/XLOOKUP Excel Tutorial File.xlsx
+++ b/XLOOKUP Excel Tutorial File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghanb\OneDrive\Desktop\excel-xlookup-data-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD8C8A2-4D4E-4F2F-B033-4E22ECEC0B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A5EA81-38D7-4C6F-9D1A-329EA9F5B332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="5" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
   </bookViews>
   <sheets>
     <sheet name="XLookUp" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2038,6 +2038,10 @@
       <c r="A3" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="B3" t="str">
+        <f>_xlfn.XLOOKUP(A3,N2:N10,I2:I10,,1)</f>
+        <v>Angela Martin</v>
+      </c>
       <c r="F3">
         <v>1002</v>
       </c>
@@ -2075,6 +2079,10 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>38</v>
+      </c>
+      <c r="B4" t="str">
+        <f>_xlfn.XLOOKUP(A4,N2:N10,I2:I10,,,-1)</f>
+        <v>Michael Scott</v>
       </c>
       <c r="F4">
         <v>1003</v>
@@ -2390,6 +2398,10 @@
       <c r="A2" t="s">
         <v>70</v>
       </c>
+      <c r="B2">
+        <f>_xlfn.XLOOKUP(I1,H1:S1,H2:S2)</f>
+        <v>310</v>
+      </c>
       <c r="G2" t="s">
         <v>70</v>
       </c>
@@ -2434,6 +2446,10 @@
       <c r="A3" t="s">
         <v>71</v>
       </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B4" si="0">_xlfn.XLOOKUP(I2,H2:S2,H3:S3)</f>
+        <v>40</v>
+      </c>
       <c r="G3" t="s">
         <v>71</v>
       </c>
@@ -2477,6 +2493,10 @@
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>84</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>118</v>
       </c>
       <c r="G4" t="s">
         <v>84</v>
@@ -2576,6 +2596,10 @@
       <c r="A2" t="s">
         <v>70</v>
       </c>
+      <c r="B2">
+        <f>_xlfn.XLOOKUP(I1,H1:S1,H2:S2)</f>
+        <v>310</v>
+      </c>
       <c r="G2" t="s">
         <v>70</v>
       </c>
@@ -2620,6 +2644,10 @@
       <c r="A3" t="s">
         <v>71</v>
       </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B4" si="0">_xlfn.XLOOKUP(I2,H2:S2,H3:S3)</f>
+        <v>40</v>
+      </c>
       <c r="G3" t="s">
         <v>71</v>
       </c>
@@ -2664,6 +2692,10 @@
       <c r="A4" t="s">
         <v>84</v>
       </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
       <c r="G4" t="s">
         <v>84</v>
       </c>
@@ -2712,6 +2744,10 @@
     <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>70</v>
+      </c>
+      <c r="B7">
+        <f>SUM(_xlfn.XLOOKUP(I1,H1:S1,H2:S2),_xlfn.XLOOKUP(J1,H1:S1,H2:S2))</f>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
